--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487714_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487714_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.5356</v>
+        <v>5.9989</v>
       </c>
       <c r="E2" t="n">
-        <v>6.6265</v>
+        <v>6.2261</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.09089999999999999</v>
+        <v>-0.2272</v>
       </c>
       <c r="G2" t="n">
         <v>6.8901</v>
@@ -610,13 +610,13 @@
         <v>1.1642</v>
       </c>
       <c r="S2" t="n">
-        <v>0.5395</v>
+        <v>0.0028</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0863</v>
+        <v>-0.3141</v>
       </c>
       <c r="U2" t="n">
-        <v>0.4531</v>
+        <v>0.3169</v>
       </c>
       <c r="V2" t="n">
         <v>-0.894</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.7239</v>
+        <v>5.7066</v>
       </c>
       <c r="E3" t="n">
-        <v>4.271</v>
+        <v>5.1719</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4529</v>
+        <v>0.5346</v>
       </c>
       <c r="G3" t="n">
         <v>5.3807</v>
@@ -688,13 +688,13 @@
         <v>2.3284</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.7463</v>
+        <v>0.2364</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.9085</v>
+        <v>-0.0076</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1622</v>
+        <v>0.244</v>
       </c>
       <c r="V3" t="n">
         <v>1.8358</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.2724</v>
+        <v>2.5989</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9406</v>
+        <v>0.24</v>
       </c>
       <c r="F4" t="n">
-        <v>2.3317</v>
+        <v>2.359</v>
       </c>
       <c r="G4" t="n">
         <v>1.7975</v>
@@ -766,13 +766,13 @@
         <v>2.5224</v>
       </c>
       <c r="S4" t="n">
-        <v>1.3405</v>
+        <v>0.6671</v>
       </c>
       <c r="T4" t="n">
-        <v>0.3779</v>
+        <v>-0.3228</v>
       </c>
       <c r="U4" t="n">
-        <v>0.9626</v>
+        <v>0.9898</v>
       </c>
       <c r="V4" t="n">
         <v>-1.2239</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.9874</v>
+        <v>2.5419</v>
       </c>
       <c r="E5" t="n">
-        <v>2.3654</v>
+        <v>2.5656</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.3779</v>
+        <v>-0.0236</v>
       </c>
       <c r="G5" t="n">
         <v>1.9258</v>
@@ -844,13 +844,13 @@
         <v>1.7463</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.0727</v>
+        <v>-0.5182</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.6415999999999999</v>
+        <v>-0.4414</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.4311</v>
+        <v>-0.07679999999999999</v>
       </c>
       <c r="V5" t="n">
         <v>-0.6119</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.3914</v>
+        <v>1.7378</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.5963000000000001</v>
+        <v>0.1044</v>
       </c>
       <c r="F6" t="n">
-        <v>1.9877</v>
+        <v>1.6334</v>
       </c>
       <c r="G6" t="n">
         <v>-0.3581</v>
@@ -922,13 +922,13 @@
         <v>1.3582</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0779</v>
+        <v>0.4242</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.9691</v>
+        <v>-0.2684</v>
       </c>
       <c r="U6" t="n">
-        <v>1.0469</v>
+        <v>0.6926</v>
       </c>
       <c r="V6" t="n">
         <v>2.4477</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.2416</v>
+        <v>0.86</v>
       </c>
       <c r="E7" t="n">
         <v>-0.2834</v>
       </c>
       <c r="F7" t="n">
-        <v>1.525</v>
+        <v>1.1434</v>
       </c>
       <c r="G7" t="n">
         <v>0.879</v>
@@ -1000,13 +1000,13 @@
         <v>2.3284</v>
       </c>
       <c r="S7" t="n">
-        <v>0.6059</v>
+        <v>0.2243</v>
       </c>
       <c r="T7" t="n">
         <v>-0.2894</v>
       </c>
       <c r="U7" t="n">
-        <v>0.8953</v>
+        <v>0.5137</v>
       </c>
       <c r="V7" t="n">
         <v>-1.6015</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.2999</v>
+        <v>0.7092000000000001</v>
       </c>
       <c r="E8" t="n">
-        <v>2.4229</v>
+        <v>2.7232</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.123</v>
+        <v>-2.014</v>
       </c>
       <c r="G8" t="n">
         <v>2.8264</v>
@@ -1078,13 +1078,13 @@
         <v>2.1344</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.8369</v>
+        <v>-0.4276</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.581</v>
+        <v>-0.2807</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2559</v>
+        <v>-0.1469</v>
       </c>
       <c r="V8" t="n">
         <v>-1.8836</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.9029</v>
+        <v>-1.3935</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.5969</v>
+        <v>-1.1965</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.306</v>
+        <v>-0.1969</v>
       </c>
       <c r="G9" t="n">
         <v>-1.8572</v>
@@ -1156,13 +1156,13 @@
         <v>1.1642</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.3277</v>
+        <v>0.1817</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.4722</v>
+        <v>-0.0718</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1445</v>
+        <v>0.2535</v>
       </c>
       <c r="V9" t="n">
         <v>0.2821</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.299</v>
+        <v>-3.3639</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.0089</v>
+        <v>-3.2101</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.2901</v>
+        <v>-0.1538</v>
       </c>
       <c r="G10" t="n">
         <v>-2.8353</v>
@@ -1234,13 +1234,13 @@
         <v>2.3284</v>
       </c>
       <c r="S10" t="n">
-        <v>1.984</v>
+        <v>0.9191</v>
       </c>
       <c r="T10" t="n">
-        <v>1.8214</v>
+        <v>0.6202</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1626</v>
+        <v>0.2989</v>
       </c>
       <c r="V10" t="n">
         <v>-1.8358</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.51</v>
+        <v>-4.6557</v>
       </c>
       <c r="E11" t="n">
-        <v>0.6478</v>
+        <v>0.4476</v>
       </c>
       <c r="F11" t="n">
-        <v>-5.1578</v>
+        <v>-5.1033</v>
       </c>
       <c r="G11" t="n">
         <v>-1.3206</v>
@@ -1312,13 +1312,13 @@
         <v>0.3881</v>
       </c>
       <c r="S11" t="n">
-        <v>0.3762</v>
+        <v>0.2305</v>
       </c>
       <c r="T11" t="n">
-        <v>0.4374</v>
+        <v>0.2372</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0612</v>
+        <v>-0.0067</v>
       </c>
       <c r="V11" t="n">
         <v>-3.9537</v>
@@ -1345,10 +1345,10 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>10.7403</v>
+        <v>10.7402</v>
       </c>
       <c r="E12" t="n">
-        <v>12.7887</v>
+        <v>12.7888</v>
       </c>
       <c r="F12" t="n">
         <v>-2.0484</v>
@@ -1390,13 +1390,13 @@
         <v>17.463</v>
       </c>
       <c r="S12" t="n">
-        <v>1.9404</v>
+        <v>1.9403</v>
       </c>
       <c r="T12" t="n">
         <v>-1.1388</v>
       </c>
       <c r="U12" t="n">
-        <v>3.079</v>
+        <v>3.079000000000001</v>
       </c>
       <c r="V12" t="n">
         <v>-7.438799999999999</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>5.3017</v>
+        <v>6.3144</v>
       </c>
       <c r="E13" t="n">
-        <v>7.122</v>
+        <v>7.6225</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.8203</v>
+        <v>-1.3081</v>
       </c>
       <c r="G13" t="n">
         <v>4.5927</v>
@@ -1468,13 +1468,13 @@
         <v>0.9702</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.5581</v>
+        <v>-0.5454</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.0902</v>
+        <v>-0.5897</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.4679</v>
+        <v>0.0443</v>
       </c>
       <c r="V13" t="n">
         <v>5.1776</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.6954</v>
+        <v>2.9323</v>
       </c>
       <c r="E14" t="n">
-        <v>2.3595</v>
+        <v>2.7599</v>
       </c>
       <c r="F14" t="n">
-        <v>0.3359</v>
+        <v>0.1724</v>
       </c>
       <c r="G14" t="n">
         <v>0.5689</v>
@@ -1546,13 +1546,13 @@
         <v>1.7463</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.2795</v>
+        <v>-0.0426</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.8479</v>
+        <v>-0.4475</v>
       </c>
       <c r="U14" t="n">
-        <v>0.5684</v>
+        <v>0.4049</v>
       </c>
       <c r="V14" t="n">
         <v>0.6597</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.5698</v>
+        <v>1.7173</v>
       </c>
       <c r="E15" t="n">
-        <v>3.8223</v>
+        <v>2.6211</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.2525</v>
+        <v>-0.9038</v>
       </c>
       <c r="G15" t="n">
         <v>-2.0982</v>
@@ -1624,13 +1624,13 @@
         <v>1.1642</v>
       </c>
       <c r="S15" t="n">
-        <v>1.6202</v>
+        <v>0.7677</v>
       </c>
       <c r="T15" t="n">
-        <v>1.5298</v>
+        <v>0.3286</v>
       </c>
       <c r="U15" t="n">
-        <v>0.09039999999999999</v>
+        <v>0.4391</v>
       </c>
       <c r="V15" t="n">
         <v>1.8836</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.1949</v>
+        <v>1.6376</v>
       </c>
       <c r="E16" t="n">
-        <v>1.7757</v>
+        <v>1.9759</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.5808</v>
+        <v>-0.3383</v>
       </c>
       <c r="G16" t="n">
         <v>0.0985</v>
@@ -1702,13 +1702,13 @@
         <v>1.9403</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.7393</v>
+        <v>-0.2967</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.0173</v>
+        <v>-0.8171</v>
       </c>
       <c r="U16" t="n">
-        <v>0.2779</v>
+        <v>0.5204</v>
       </c>
       <c r="V16" t="n">
         <v>1.8358</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.7984</v>
+        <v>0.9167999999999999</v>
       </c>
       <c r="E17" t="n">
-        <v>0.7726</v>
+        <v>0.9728</v>
       </c>
       <c r="F17" t="n">
-        <v>0.0257</v>
+        <v>-0.056</v>
       </c>
       <c r="G17" t="n">
         <v>0.5018</v>
@@ -1780,13 +1780,13 @@
         <v>0.5821</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.2855</v>
+        <v>-0.1671</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.3028</v>
+        <v>-0.1026</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0173</v>
+        <v>-0.0645</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>G. GOMA</t>
+          <t>J. VAQUERO PASCUAL</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.1532</v>
+        <v>-2.0268</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.5591</v>
+        <v>-2.5115</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.5941</v>
+        <v>0.4847</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.4751</v>
+        <v>-0.8605</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.3132</v>
+        <v>0.3518</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.1619</v>
+        <v>-1.2123</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.2788</v>
+        <v>-0.3913</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.4005</v>
+        <v>0.9434</v>
       </c>
       <c r="L18" t="n">
-        <v>0.1218</v>
+        <v>-1.3347</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.1963</v>
+        <v>-0.4692</v>
       </c>
       <c r="N18" t="n">
-        <v>0.0873</v>
+        <v>-0.5916</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.2836</v>
+        <v>0.1223</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.5821</v>
+        <v>-3.1045</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.9403</v>
+        <v>-3.8806</v>
       </c>
       <c r="R18" t="n">
-        <v>1.3582</v>
+        <v>0.7761</v>
       </c>
       <c r="S18" t="n">
-        <v>2.1279</v>
+        <v>-0.5095</v>
       </c>
       <c r="T18" t="n">
-        <v>1.1541</v>
+        <v>-0.6873</v>
       </c>
       <c r="U18" t="n">
-        <v>0.9738</v>
+        <v>0.1778</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.2239</v>
+        <v>2.4477</v>
       </c>
       <c r="W18" t="n">
-        <v>1.506</v>
+        <v>2.4477</v>
       </c>
       <c r="X18" t="n">
-        <v>-2.7298</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. VAQUERO PASCUAL</t>
+          <t>D. VAL GUTIERREZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.5056</v>
+        <v>-2.5219</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.6116</v>
+        <v>-1.503</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1059</v>
+        <v>-1.0189</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.8605</v>
+        <v>-2.2516</v>
       </c>
       <c r="H19" t="n">
-        <v>0.3518</v>
+        <v>-0.0354</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.2123</v>
+        <v>-2.2161</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.3913</v>
+        <v>-1.0369</v>
       </c>
       <c r="K19" t="n">
-        <v>0.9434</v>
+        <v>0.7621</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.3347</v>
+        <v>-1.799</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.4692</v>
+        <v>-1.2146</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.5916</v>
+        <v>-0.7975</v>
       </c>
       <c r="O19" t="n">
-        <v>0.1223</v>
+        <v>-0.4171</v>
       </c>
       <c r="P19" t="n">
-        <v>-3.1045</v>
+        <v>0.7761</v>
       </c>
       <c r="Q19" t="n">
-        <v>-3.8806</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
         <v>0.7761</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.9883</v>
+        <v>-0.4823</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.7874</v>
+        <v>-0.466</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.201</v>
+        <v>-0.0162</v>
       </c>
       <c r="V19" t="n">
-        <v>2.4477</v>
+        <v>-0.5642</v>
       </c>
       <c r="W19" t="n">
-        <v>2.4477</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-0.5642</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>D. VAL GUTIERREZ</t>
+          <t>G. GOMA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.7493</v>
+        <v>-2.672</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.7032</v>
+        <v>-1.5601</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.0462</v>
+        <v>-1.112</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.2516</v>
+        <v>-1.4751</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.0354</v>
+        <v>-1.3132</v>
       </c>
       <c r="I20" t="n">
-        <v>-2.2161</v>
+        <v>-0.1619</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.0369</v>
+        <v>-1.2788</v>
       </c>
       <c r="K20" t="n">
-        <v>0.7621</v>
+        <v>-1.4005</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.799</v>
+        <v>0.1218</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.2146</v>
+        <v>-0.1963</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.7975</v>
+        <v>0.0873</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.4171</v>
+        <v>-0.2836</v>
       </c>
       <c r="P20" t="n">
-        <v>0.7761</v>
+        <v>-0.5821</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-1.9403</v>
       </c>
       <c r="R20" t="n">
-        <v>0.7761</v>
+        <v>1.3582</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.7097</v>
+        <v>0.609</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.6662</v>
+        <v>0.1531</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0435</v>
+        <v>0.456</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.5642</v>
+        <v>-1.2239</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.506</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.5642</v>
+        <v>-2.7298</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.7285</v>
+        <v>-3.0583</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.3814</v>
+        <v>0.019</v>
       </c>
       <c r="F21" t="n">
-        <v>-3.3471</v>
+        <v>-3.0773</v>
       </c>
       <c r="G21" t="n">
         <v>-2.5141</v>
@@ -2092,13 +2092,13 @@
         <v>1.7463</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.0487</v>
+        <v>-0.3785</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.775</v>
+        <v>-0.3746</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.2736</v>
+        <v>-0.0039</v>
       </c>
       <c r="V21" t="n">
         <v>-0.9418</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-5.1755</v>
+        <v>-4.3625</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.4651</v>
+        <v>-3.8645</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.7104</v>
+        <v>-0.498</v>
       </c>
       <c r="G22" t="n">
         <v>-5.8301</v>
@@ -2170,13 +2170,13 @@
         <v>2.3284</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.7037</v>
+        <v>0.1093</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.0779</v>
+        <v>-0.4773</v>
       </c>
       <c r="U22" t="n">
-        <v>0.3742</v>
+        <v>0.5866</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-7.9883</v>
+        <v>-8.282500000000001</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.0833</v>
+        <v>-4.4837</v>
       </c>
       <c r="F23" t="n">
-        <v>-3.905</v>
+        <v>-3.7988</v>
       </c>
       <c r="G23" t="n">
         <v>-4.0606</v>
@@ -2248,13 +2248,13 @@
         <v>1.1642</v>
       </c>
       <c r="S23" t="n">
-        <v>0.6245000000000001</v>
+        <v>0.3303</v>
       </c>
       <c r="T23" t="n">
-        <v>0.8018999999999999</v>
+        <v>0.4015</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.1774</v>
+        <v>-0.0712</v>
       </c>
       <c r="V23" t="n">
         <v>-1.8358</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-10.7402</v>
+        <v>-9.4056</v>
       </c>
       <c r="E24" t="n">
-        <v>2.0484</v>
+        <v>2.048400000000002</v>
       </c>
       <c r="F24" t="n">
-        <v>-12.7889</v>
+        <v>-11.4541</v>
       </c>
       <c r="G24" t="n">
         <v>-13.3283</v>
@@ -2299,13 +2299,13 @@
         <v>-6.0617</v>
       </c>
       <c r="J24" t="n">
-        <v>7.387499999999999</v>
+        <v>7.387500000000001</v>
       </c>
       <c r="K24" t="n">
         <v>6.5252</v>
       </c>
       <c r="L24" t="n">
-        <v>0.8621999999999996</v>
+        <v>0.8622000000000005</v>
       </c>
       <c r="M24" t="n">
         <v>-20.7156</v>
@@ -2326,13 +2326,13 @@
         <v>14.5524</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.9402</v>
+        <v>-0.6058000000000001</v>
       </c>
       <c r="T24" t="n">
         <v>-3.0789</v>
       </c>
       <c r="U24" t="n">
-        <v>1.1386</v>
+        <v>2.4733</v>
       </c>
       <c r="V24" t="n">
         <v>7.4387</v>
